--- a/data/dividends_info_20261002.xlsx
+++ b/data/dividends_info_20261002.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>48.99499893188477</v>
+        <v>50.34000015258789</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1836922174957538</v>
+        <v>0.1787842664425841</v>
       </c>
       <c r="J2" t="n">
         <v>164</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>61.84999847412109</v>
+        <v>62</v>
       </c>
       <c r="I3" t="n">
-        <v>1.131770440209291</v>
+        <v>1.129032258064516</v>
       </c>
       <c r="J3" t="n">
         <v>143</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.880000114440918</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6756756669679118</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J4" t="n">
         <v>73</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49.00500106811523</v>
+        <v>50.34000015258789</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1836547251063277</v>
+        <v>0.1787842664425841</v>
       </c>
       <c r="J6" t="n">
         <v>73</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.019999980926514</v>
+        <v>2.025000095367432</v>
       </c>
       <c r="I7" t="n">
-        <v>3.811881224111814</v>
+        <v>3.802468956725087</v>
       </c>
       <c r="J7" t="n">
         <v>52</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>49.09999847412109</v>
+        <v>48.77999877929688</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6313645817390203</v>
+        <v>0.6355063709668842</v>
       </c>
       <c r="J8" t="n">
         <v>52</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.9950008392334</v>
+        <v>24.19000053405762</v>
       </c>
       <c r="I9" t="n">
-        <v>1.125234384482839</v>
+        <v>1.116163679367684</v>
       </c>
       <c r="J9" t="n">
         <v>52</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>24.53000068664551</v>
+        <v>24.73999977111816</v>
       </c>
       <c r="I10" t="n">
-        <v>2.40521803295833</v>
+        <v>2.384801962240819</v>
       </c>
       <c r="J10" t="n">
         <v>52</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.72000026702881</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="I11" t="n">
-        <v>1.791808832895514</v>
+        <v>1.813471514538592</v>
       </c>
       <c r="J11" t="n">
         <v>45</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.800000190734863</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I12" t="n">
-        <v>3.44827574867131</v>
+        <v>3.436426015480821</v>
       </c>
       <c r="J12" t="n">
         <v>45</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.849999904632568</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I13" t="n">
-        <v>1.196581216088013</v>
+        <v>1.176470625948566</v>
       </c>
       <c r="J13" t="n">
         <v>38</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.25</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6486486486486486</v>
+        <v>0.6772009291759016</v>
       </c>
       <c r="J14" t="n">
         <v>38</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.52000045776367</v>
+        <v>10.47999954223633</v>
       </c>
       <c r="I15" t="n">
-        <v>4.372623383875653</v>
+        <v>4.389313168823293</v>
       </c>
       <c r="J15" t="n">
         <v>24</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.600000381469727</v>
+        <v>8.75</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6976743876579468</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="J16" t="n">
         <v>17</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.9689922767163736</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.119999885559082</v>
+        <v>7.920000076293945</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4679803021620808</v>
+        <v>0.4797979751760504</v>
       </c>
       <c r="J19" t="n">
         <v>-4</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23.9950008392334</v>
+        <v>24.19000053405762</v>
       </c>
       <c r="I20" t="n">
-        <v>1.125234384482839</v>
+        <v>1.116163679367684</v>
       </c>
       <c r="J20" t="n">
         <v>-11</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.876999974250793</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="I21" t="n">
-        <v>3.036760830151402</v>
+        <v>3.031914901307073</v>
       </c>
       <c r="J21" t="n">
         <v>-11</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>49.00500106811523</v>
+        <v>50.34000015258789</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1836547251063277</v>
+        <v>0.1787842664425841</v>
       </c>
       <c r="J22" t="n">
         <v>-11</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>93.90000152587891</v>
+        <v>93.34999847412109</v>
       </c>
       <c r="I23" t="n">
-        <v>1.416400402968525</v>
+        <v>1.424745604434807</v>
       </c>
       <c r="J23" t="n">
         <v>-11</v>
@@ -1580,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2334,7 +2334,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2351,7 +2351,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2412,14 +2412,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2436,7 +2436,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2446,14 +2446,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2582,14 +2582,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2599,14 +2599,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2623,7 +2623,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2633,14 +2633,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2725,7 +2725,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2793,63 +2793,63 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2871,14 +2871,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2888,36 +2888,36 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2929,12 +2929,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2946,29 +2946,29 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2980,63 +2980,63 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3048,12 +3048,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3065,29 +3065,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3099,270 +3099,15 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Italgas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Italgas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>EDISON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
@@ -3392,95 +3137,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Arterra Bioscience S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Dedem S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ESPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>